--- a/samples/tracking01/tracking05.xlsx
+++ b/samples/tracking01/tracking05.xlsx
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
